--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1908,7 +1908,7 @@
         <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80174</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4669,7 +4669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115859</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530097</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4786,7 +4786,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115856</v>
       </c>
       <c r="B35" t="n">
         <v>57723</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529991</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5150,7 +5150,7 @@
         <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>92308</v>
+        <v>92313</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5797,39 +5797,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,10 +5913,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5914,34 +5924,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115874</v>
+        <v>129115895</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,39 +6519,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530014</v>
+        <v>530122</v>
       </c>
       <c r="R49" t="n">
-        <v>7179668</v>
+        <v>7179836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6583,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6593,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6609,6 +6604,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6625,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115930</v>
+        <v>129115899</v>
       </c>
       <c r="B50" t="n">
-        <v>91538</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6636,21 +6646,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6660,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530065</v>
+        <v>530013</v>
       </c>
       <c r="R50" t="n">
-        <v>7179830</v>
+        <v>7179829</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6695,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6705,12 +6715,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6724,17 +6734,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6752,10 +6762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115912</v>
+        <v>129115930</v>
       </c>
       <c r="B51" t="n">
-        <v>80140</v>
+        <v>91541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6763,21 +6773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6787,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530071</v>
+        <v>530065</v>
       </c>
       <c r="R51" t="n">
-        <v>7179681</v>
+        <v>7179830</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6822,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6832,12 +6842,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6851,17 +6861,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6879,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115878</v>
+        <v>129115912</v>
       </c>
       <c r="B52" t="n">
         <v>80140</v>
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529899</v>
+        <v>530071</v>
       </c>
       <c r="R52" t="n">
-        <v>7179626</v>
+        <v>7179681</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6949,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6959,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7006,7 +7016,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115895</v>
+        <v>129115878</v>
       </c>
       <c r="B53" t="n">
         <v>80140</v>
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530122</v>
+        <v>529899</v>
       </c>
       <c r="R53" t="n">
-        <v>7179836</v>
+        <v>7179626</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7076,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7086,7 +7096,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7133,10 +7143,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115899</v>
+        <v>129115874</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7144,34 +7154,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530013</v>
+        <v>530014</v>
       </c>
       <c r="R54" t="n">
-        <v>7179829</v>
+        <v>7179668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7203,7 +7218,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7213,12 +7228,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7229,21 +7244,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7517,7 +7517,7 @@
         <v>129115927</v>
       </c>
       <c r="B57" t="n">
-        <v>91516</v>
+        <v>91519</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115905</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530120</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115923</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>529957</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1269,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1420,7 +1420,7 @@
         <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129115907</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129115913</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129115890</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>129115910</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>129115903</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>129115883</v>
       </c>
       <c r="B25" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129115925</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>129115886</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>129115921</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>129115918</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>129115892</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>129115891</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115859</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
         <v>57723</v>
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530097</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4786,7 +4786,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115856</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
         <v>57723</v>
@@ -4826,10 +4826,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529991</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>129115885</v>
       </c>
       <c r="B36" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5147,45 +5147,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>92313</v>
+        <v>80141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5230,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5241,22 +5244,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,10 +5278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>92316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80174</v>
+        <v>80141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5797,34 +5797,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,50 +5903,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6384,7 +6384,7 @@
         <v>129115888</v>
       </c>
       <c r="B48" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115895</v>
+        <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530122</v>
+        <v>530065</v>
       </c>
       <c r="R49" t="n">
-        <v>7179836</v>
+        <v>7179830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115899</v>
+        <v>129115874</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6646,34 +6646,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530013</v>
+        <v>530014</v>
       </c>
       <c r="R50" t="n">
-        <v>7179829</v>
+        <v>7179668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6710,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,12 +6720,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6731,21 +6736,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6762,10 +6752,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B51" t="n">
-        <v>91541</v>
+        <v>80141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6773,21 +6763,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6797,10 +6787,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R51" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6822,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,12 +6832,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6861,17 +6851,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6889,10 +6879,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115912</v>
+        <v>129115878</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6924,10 +6914,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530071</v>
+        <v>529899</v>
       </c>
       <c r="R52" t="n">
-        <v>7179681</v>
+        <v>7179626</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6949,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6959,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7016,10 +7006,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115878</v>
+        <v>129115895</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7051,10 +7041,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529899</v>
+        <v>530122</v>
       </c>
       <c r="R53" t="n">
-        <v>7179626</v>
+        <v>7179836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7076,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,7 +7086,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7143,10 +7133,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115874</v>
+        <v>129115899</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7154,39 +7144,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530014</v>
+        <v>530013</v>
       </c>
       <c r="R54" t="n">
-        <v>7179668</v>
+        <v>7179829</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7218,7 +7203,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7228,12 +7213,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7244,6 +7229,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7263,7 +7263,7 @@
         <v>129115887</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>129115896</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7514,10 +7514,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115927</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
-        <v>91519</v>
+        <v>80141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530130</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179707</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115884</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529906</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179662</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7768,10 +7768,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115908</v>
+        <v>129115927</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>91522</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7779,21 +7779,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530106</v>
+        <v>530130</v>
       </c>
       <c r="R59" t="n">
-        <v>7179677</v>
+        <v>7179707</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7867,17 +7867,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7898,7 +7898,7 @@
         <v>129115919</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>80141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,7 +1056,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115905</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
         <v>80141</v>
@@ -1081,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530120</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179702</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115923</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529957</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179580</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115883</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529906</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179662</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115921</v>
       </c>
       <c r="B27" t="n">
         <v>80141</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>529933</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115918</v>
       </c>
       <c r="B28" t="n">
         <v>80141</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>529944</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115918</v>
+        <v>129115892</v>
       </c>
       <c r="B29" t="n">
         <v>80141</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529944</v>
+        <v>530133</v>
       </c>
       <c r="R29" t="n">
-        <v>7179679</v>
+        <v>7179885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115892</v>
+        <v>129115883</v>
       </c>
       <c r="B30" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530133</v>
+        <v>529906</v>
       </c>
       <c r="R30" t="n">
-        <v>7179885</v>
+        <v>7179662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115859</v>
       </c>
       <c r="B32" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,34 +4416,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>530097</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4480,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,12 +4490,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4511,21 +4506,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4542,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80141</v>
@@ -4577,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4660,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530042</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4745,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4787,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529983</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4846,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4856,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5786,50 +5786,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,45 +5913,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115930</v>
+        <v>129115874</v>
       </c>
       <c r="B49" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,34 +6519,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R49" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6583,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6593,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6604,21 +6609,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6635,10 +6625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115874</v>
+        <v>129115930</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6646,39 +6636,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R50" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6710,7 +6695,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6720,12 +6705,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6736,6 +6721,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7514,10 +7514,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B57" t="n">
-        <v>80141</v>
+        <v>91522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7525,21 +7525,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B58" t="n">
         <v>80141</v>
@@ -7676,10 +7676,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7768,10 +7768,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B59" t="n">
-        <v>91522</v>
+        <v>80141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7779,21 +7779,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R59" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7867,17 +7867,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B60" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7906,34 +7906,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R60" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7965,7 +7970,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7975,12 +7980,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7991,21 +7996,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8022,10 +8012,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8033,39 +8023,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R61" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8097,7 +8082,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8107,12 +8092,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8123,6 +8108,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115921</v>
+        <v>129115918</v>
       </c>
       <c r="B27" t="n">
         <v>80141</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529933</v>
+        <v>529944</v>
       </c>
       <c r="R27" t="n">
-        <v>7179634</v>
+        <v>7179679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115918</v>
+        <v>129115892</v>
       </c>
       <c r="B28" t="n">
         <v>80141</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529944</v>
+        <v>530133</v>
       </c>
       <c r="R28" t="n">
-        <v>7179679</v>
+        <v>7179885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,10 +4034,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B29" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4045,21 +4045,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R29" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115874</v>
+        <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,39 +6519,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R49" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6583,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6593,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6609,6 +6604,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6625,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115930</v>
+        <v>129115874</v>
       </c>
       <c r="B50" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6636,34 +6646,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R50" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6695,7 +6710,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6705,12 +6720,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6721,21 +6736,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7895,10 +7895,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7906,39 +7906,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R60" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7970,7 +7965,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7980,12 +7975,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7996,6 +7991,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8012,10 +8022,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B61" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8023,34 +8033,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R61" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8082,7 +8097,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8092,12 +8107,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8108,21 +8123,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80141</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B5" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1259,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1386,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B8" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,21 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
         <v>80141</v>
@@ -1579,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1671,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115864</v>
+        <v>129115907</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,39 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530219</v>
+        <v>530117</v>
       </c>
       <c r="R10" t="n">
-        <v>7179873</v>
+        <v>7179681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,6 +1757,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,45 +1788,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,21 +1889,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1915,50 +1905,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80141</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,7 +3272,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
         <v>80141</v>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115925</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529940</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179623</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115883</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529906</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179662</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115859</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,39 +4426,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530097</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179880</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4490,12 +4495,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4506,6 +4511,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80141</v>
@@ -4557,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115901</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4660,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530042</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4745,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115891</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4797,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529983</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,12 +4871,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B42" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5670,34 +5670,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5734,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5744,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5755,21 +5760,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5786,32 +5776,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>80141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5821,10 +5811,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5846,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5856,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5913,50 +5903,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>91544</v>
+        <v>80141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115874</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6646,39 +6646,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530014</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179668</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6710,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6720,12 +6715,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6736,6 +6731,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6752,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115912</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
         <v>80141</v>
@@ -6787,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530071</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179681</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6822,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6832,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6879,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115878</v>
+        <v>129115899</v>
       </c>
       <c r="B52" t="n">
         <v>80141</v>
@@ -6914,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529899</v>
+        <v>530013</v>
       </c>
       <c r="R52" t="n">
-        <v>7179626</v>
+        <v>7179829</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6949,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6959,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7006,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115895</v>
+        <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>80141</v>
+        <v>91544</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7017,21 +7027,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530122</v>
+        <v>530065</v>
       </c>
       <c r="R53" t="n">
-        <v>7179836</v>
+        <v>7179830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7076,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7086,12 +7096,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7105,17 +7115,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7133,7 +7143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115899</v>
+        <v>129115887</v>
       </c>
       <c r="B54" t="n">
         <v>80141</v>
@@ -7168,10 +7178,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530013</v>
+        <v>529887</v>
       </c>
       <c r="R54" t="n">
-        <v>7179829</v>
+        <v>7179641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7203,7 +7213,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7213,7 +7223,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7260,7 +7270,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129115887</v>
+        <v>129115896</v>
       </c>
       <c r="B55" t="n">
         <v>80141</v>
@@ -7295,10 +7305,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529887</v>
+        <v>530106</v>
       </c>
       <c r="R55" t="n">
-        <v>7179641</v>
+        <v>7179857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7330,7 +7340,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7340,7 +7350,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7387,7 +7397,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115896</v>
+        <v>129115884</v>
       </c>
       <c r="B56" t="n">
         <v>80141</v>
@@ -7422,10 +7432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R56" t="n">
-        <v>7179857</v>
+        <v>7179662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7457,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7467,7 +7477,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7514,10 +7524,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B57" t="n">
-        <v>91522</v>
+        <v>80141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7525,21 +7535,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7549,10 +7559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R57" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7584,7 +7594,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7594,12 +7604,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7613,17 +7623,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,10 +7651,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B58" t="n">
-        <v>80141</v>
+        <v>91522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7652,21 +7662,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7676,10 +7686,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R58" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7711,7 +7721,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7721,12 +7731,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7740,17 +7750,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7768,10 +7778,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115908</v>
+        <v>129115867</v>
       </c>
       <c r="B59" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7779,34 +7789,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530106</v>
+        <v>530121</v>
       </c>
       <c r="R59" t="n">
-        <v>7179677</v>
+        <v>7179847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7838,7 +7853,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7848,12 +7863,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7864,21 +7879,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -8022,10 +8022,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129115867</v>
+        <v>129115855</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8051,21 +8051,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>530121</v>
+        <v>530228</v>
       </c>
       <c r="R61" t="n">
-        <v>7179847</v>
+        <v>7179919</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8097,7 +8100,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8107,12 +8110,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Bohål gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8136,6 +8139,239 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129115874</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ytter-rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>530014</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7179668</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129115928</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ytter-rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>530065</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7179830</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>80145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1152,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>57722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1311,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,21 +1401,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115864</v>
+        <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,39 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530219</v>
+        <v>530065</v>
       </c>
       <c r="R8" t="n">
-        <v>7179873</v>
+        <v>7179640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1513,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115907</v>
       </c>
       <c r="B9" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>530117</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1661,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115907</v>
+        <v>129115864</v>
       </c>
       <c r="B10" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,34 +1682,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530117</v>
+        <v>530219</v>
       </c>
       <c r="R10" t="n">
-        <v>7179681</v>
+        <v>7179873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,21 +1772,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,7 +1791,7 @@
         <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B13" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B14" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,34 +2170,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2234,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,12 +2244,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2255,21 +2260,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2406,7 +2406,7 @@
         <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129115890</v>
       </c>
       <c r="B17" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>129115910</v>
       </c>
       <c r="B18" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>129115871</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80141</v>
+        <v>80179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,10 +3282,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B23" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,34 +3420,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530122</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,21 +3510,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3529,7 +3529,7 @@
         <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115892</v>
       </c>
       <c r="B26" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>530133</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,32 +3780,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115918</v>
+        <v>129115883</v>
       </c>
       <c r="B27" t="n">
-        <v>80141</v>
+        <v>80179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529944</v>
+        <v>529906</v>
       </c>
       <c r="R27" t="n">
-        <v>7179679</v>
+        <v>7179662</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B28" t="n">
-        <v>80141</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R28" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115921</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>80145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>529933</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179634</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115918</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>80145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>529944</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4291,7 +4291,7 @@
         <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>129115891</v>
       </c>
       <c r="B33" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>129115885</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129115860</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5147,48 +5147,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80141</v>
+        <v>92323</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5244,23 +5241,22 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5278,10 +5274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5307,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5348,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5358,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5372,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
-        <v>92316</v>
+        <v>80145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5670,39 +5670,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5734,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5744,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,6 +5755,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5776,32 +5786,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>80141</v>
+        <v>80179</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5811,10 +5821,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5846,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5856,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5903,45 +5913,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6033,7 +6033,7 @@
         <v>129115872</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>129115857</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>129115865</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>129115888</v>
       </c>
       <c r="B48" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129115878</v>
       </c>
       <c r="B50" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>129115895</v>
       </c>
       <c r="B51" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>129115899</v>
       </c>
       <c r="B52" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>129115887</v>
       </c>
       <c r="B54" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>129115896</v>
       </c>
       <c r="B55" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>80141</v>
+        <v>91529</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R56" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7651,10 +7651,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>91522</v>
+        <v>80145</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7662,21 +7662,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7789,39 +7789,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R59" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7853,7 +7848,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7863,12 +7858,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7879,6 +7874,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7895,10 +7905,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B60" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7906,34 +7916,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R60" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7965,7 +7980,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7975,12 +7990,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7991,21 +8006,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8142,53 +8142,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>91894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8220,7 +8212,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8230,12 +8222,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8244,6 +8236,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8262,45 +8255,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>91892</v>
+        <v>57725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8332,7 +8333,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8342,12 +8343,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8356,7 +8357,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>92233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,45 +5786,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80179</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,10 +5903,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5924,39 +5914,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>80145</v>
+        <v>91551</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>530065</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B53" t="n">
-        <v>91551</v>
+        <v>80145</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R53" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80145</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115905</v>
       </c>
       <c r="B5" t="n">
         <v>80145</v>
@@ -1091,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530120</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115923</v>
       </c>
       <c r="B6" t="n">
-        <v>57722</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>529957</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1269,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1417,7 +1417,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115907</v>
       </c>
       <c r="B8" t="n">
         <v>80145</v>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530117</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1544,7 +1544,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
         <v>80145</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1791,7 +1791,7 @@
         <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
         <v>80145</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,39 +2170,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2234,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2244,12 +2239,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,6 +2255,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3653,7 +3653,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115892</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
         <v>80145</v>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530133</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179885</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,32 +3780,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115883</v>
+        <v>129115892</v>
       </c>
       <c r="B27" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529906</v>
+        <v>530133</v>
       </c>
       <c r="R27" t="n">
-        <v>7179662</v>
+        <v>7179885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115925</v>
+        <v>129115918</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529940</v>
+        <v>529944</v>
       </c>
       <c r="R28" t="n">
-        <v>7179623</v>
+        <v>7179679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115921</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529933</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179634</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115918</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529944</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179679</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4669,10 +4659,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4670,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4729,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4739,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4755,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5147,32 +5147,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115924</v>
       </c>
       <c r="B38" t="n">
-        <v>92323</v>
+        <v>80145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>529939</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5405,32 +5405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115926</v>
       </c>
       <c r="B40" t="n">
-        <v>80145</v>
+        <v>92330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>530129</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115881</v>
       </c>
       <c r="B41" t="n">
         <v>80145</v>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530093</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80179</v>
+        <v>80145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5903,32 +5903,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>80145</v>
+        <v>80179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6030,7 +6030,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129115872</v>
+        <v>129115857</v>
       </c>
       <c r="B45" t="n">
         <v>57725</v>
@@ -6061,7 +6061,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530030</v>
+        <v>529996</v>
       </c>
       <c r="R45" t="n">
-        <v>7179843</v>
+        <v>7179837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129115857</v>
+        <v>129115872</v>
       </c>
       <c r="B46" t="n">
         <v>57725</v>
@@ -6178,7 +6178,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529996</v>
+        <v>530030</v>
       </c>
       <c r="R46" t="n">
-        <v>7179837</v>
+        <v>7179843</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6511,7 +6511,7 @@
         <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115912</v>
       </c>
       <c r="B50" t="n">
         <v>80145</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530071</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115878</v>
       </c>
       <c r="B51" t="n">
         <v>80145</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>529899</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179626</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7016,7 +7016,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115912</v>
+        <v>129115895</v>
       </c>
       <c r="B53" t="n">
         <v>80145</v>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530071</v>
+        <v>530122</v>
       </c>
       <c r="R53" t="n">
-        <v>7179681</v>
+        <v>7179836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7397,10 +7397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B56" t="n">
-        <v>91529</v>
+        <v>80145</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R56" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B57" t="n">
-        <v>80145</v>
+        <v>91536</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7535,21 +7535,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7651,7 +7651,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B58" t="n">
         <v>80145</v>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8145,7 +8145,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91894</v>
+        <v>91901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80179</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>80147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115905</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530120</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179702</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115923</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529957</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179580</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1303,7 +1303,7 @@
         <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R8" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1544,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115907</v>
       </c>
       <c r="B9" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>530117</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1674,7 +1674,7 @@
         <v>129115864</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,34 +2043,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,21 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2159,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2406,7 +2406,7 @@
         <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129115890</v>
       </c>
       <c r="B17" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>129115910</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>129115871</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80179</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3158,7 +3158,7 @@
         <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>129115903</v>
       </c>
       <c r="B23" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115892</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>530133</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,32 +3653,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115883</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>529906</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R27" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115918</v>
+        <v>129115886</v>
       </c>
       <c r="B28" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529944</v>
+        <v>529943</v>
       </c>
       <c r="R28" t="n">
-        <v>7179679</v>
+        <v>7179577</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115921</v>
       </c>
       <c r="B29" t="n">
-        <v>80179</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>529933</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179634</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115918</v>
       </c>
       <c r="B30" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>529944</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4408,7 +4418,7 @@
         <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4535,7 +4545,7 @@
         <v>129115891</v>
       </c>
       <c r="B33" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4659,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4670,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4729,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4739,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4755,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4789,7 +4789,7 @@
         <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>129115885</v>
       </c>
       <c r="B36" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>129115860</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115924</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5176,16 +5176,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529939</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179590</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,7 +5230,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5241,6 +5244,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5274,10 +5278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,32 +5405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115926</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
-        <v>92330</v>
+        <v>80147</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530129</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179716</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115881</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80145</v>
+        <v>92332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530093</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179801</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B42" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5670,34 +5670,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5734,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5744,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5755,21 +5760,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5786,10 +5776,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5797,39 +5787,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5846,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5856,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5872,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5906,7 +5906,7 @@
         <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129115857</v>
+        <v>129115872</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529996</v>
+        <v>530030</v>
       </c>
       <c r="R45" t="n">
-        <v>7179837</v>
+        <v>7179843</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129115872</v>
+        <v>129115857</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6187,10 +6187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>530030</v>
+        <v>529996</v>
       </c>
       <c r="R46" t="n">
-        <v>7179843</v>
+        <v>7179837</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6267,7 +6267,7 @@
         <v>129115865</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>129115888</v>
       </c>
       <c r="B48" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>91558</v>
+        <v>80147</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,21 +6519,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115912</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530071</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179681</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,10 +6762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115878</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529899</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179626</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6892,7 +6892,7 @@
         <v>129115899</v>
       </c>
       <c r="B52" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115895</v>
+        <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>80145</v>
+        <v>91560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530122</v>
+        <v>530065</v>
       </c>
       <c r="R53" t="n">
-        <v>7179836</v>
+        <v>7179830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7146,7 +7146,7 @@
         <v>129115887</v>
       </c>
       <c r="B54" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>129115896</v>
       </c>
       <c r="B55" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B56" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R56" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7524,10 +7524,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B57" t="n">
-        <v>91536</v>
+        <v>80147</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7535,21 +7535,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R57" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B58" t="n">
-        <v>80145</v>
+        <v>91538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7662,21 +7662,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R58" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7778,10 +7778,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B59" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7789,34 +7789,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R59" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7848,7 +7853,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7858,12 +7863,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7874,21 +7879,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7905,10 +7895,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7916,39 +7906,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R60" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7980,7 +7965,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7990,12 +7975,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8006,6 +7991,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8025,7 +8025,7 @@
         <v>129115855</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8142,45 +8142,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B62" t="n">
-        <v>91901</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R62" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8212,7 +8220,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8222,12 +8230,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8236,7 +8244,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8255,53 +8262,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>91903</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R63" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8333,7 +8332,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8343,12 +8342,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8357,6 +8356,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80147</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1259,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1386,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +2043,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,12 +2112,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,6 +2128,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2149,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
         <v>80147</v>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115892</v>
+        <v>129115883</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530133</v>
+        <v>529906</v>
       </c>
       <c r="R25" t="n">
-        <v>7179885</v>
+        <v>7179662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,32 +3653,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115883</v>
+        <v>129115925</v>
       </c>
       <c r="B26" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529906</v>
+        <v>529940</v>
       </c>
       <c r="R26" t="n">
-        <v>7179662</v>
+        <v>7179623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115925</v>
+        <v>129115886</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3791,21 +3791,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529940</v>
+        <v>529943</v>
       </c>
       <c r="R27" t="n">
-        <v>7179623</v>
+        <v>7179577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115886</v>
+        <v>129115921</v>
       </c>
       <c r="B28" t="n">
         <v>80147</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529943</v>
+        <v>529933</v>
       </c>
       <c r="R28" t="n">
-        <v>7179577</v>
+        <v>7179634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,7 +4034,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115921</v>
+        <v>129115918</v>
       </c>
       <c r="B29" t="n">
         <v>80147</v>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529933</v>
+        <v>529944</v>
       </c>
       <c r="R29" t="n">
-        <v>7179634</v>
+        <v>7179679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,7 +4161,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115918</v>
+        <v>129115892</v>
       </c>
       <c r="B30" t="n">
         <v>80147</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529944</v>
+        <v>530133</v>
       </c>
       <c r="R30" t="n">
-        <v>7179679</v>
+        <v>7179885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5659,50 +5659,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5734,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5744,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,6 +5755,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5903,45 +5913,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,7 +6508,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115895</v>
       </c>
       <c r="B49" t="n">
         <v>80147</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>530122</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179836</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115899</v>
       </c>
       <c r="B50" t="n">
         <v>80147</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530013</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179829</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,10 +6762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115930</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>91560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6773,21 +6773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>530065</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179830</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115899</v>
+        <v>129115912</v>
       </c>
       <c r="B52" t="n">
         <v>80147</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530013</v>
+        <v>530071</v>
       </c>
       <c r="R52" t="n">
-        <v>7179829</v>
+        <v>7179681</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115930</v>
+        <v>129115878</v>
       </c>
       <c r="B53" t="n">
-        <v>91560</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530065</v>
+        <v>529899</v>
       </c>
       <c r="R53" t="n">
-        <v>7179830</v>
+        <v>7179626</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8142,53 +8142,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91903</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8220,7 +8212,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8230,12 +8222,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8244,6 +8236,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8262,45 +8255,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>91903</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8332,7 +8333,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8342,12 +8343,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8356,7 +8357,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -7778,10 +7778,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7789,39 +7789,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R59" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7853,7 +7848,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7863,12 +7858,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7879,6 +7874,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7895,10 +7905,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B60" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7906,34 +7916,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R60" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7965,7 +7980,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7975,12 +7990,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7991,21 +8006,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>80147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1152,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80147</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1311,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,21 +1401,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B8" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,21 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
         <v>80147</v>
@@ -1579,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1671,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115864</v>
+        <v>129115907</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,39 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530219</v>
+        <v>530117</v>
       </c>
       <c r="R10" t="n">
-        <v>7179873</v>
+        <v>7179681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,6 +1757,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,7 +1791,7 @@
         <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,7 +3272,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
         <v>80147</v>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115883</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529906</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179662</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115892</v>
       </c>
       <c r="B27" t="n">
         <v>80147</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>530133</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115918</v>
       </c>
       <c r="B28" t="n">
         <v>80147</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>529944</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115918</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529944</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179679</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,7 +4288,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115901</v>
       </c>
       <c r="B31" t="n">
         <v>80147</v>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>530042</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179851</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4415,7 +4415,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115891</v>
       </c>
       <c r="B32" t="n">
         <v>80147</v>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>529983</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4542,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80147</v>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115924</v>
       </c>
       <c r="B38" t="n">
         <v>80147</v>
@@ -5176,19 +5176,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>529939</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,7 +5227,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5244,7 +5241,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5278,7 +5274,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
         <v>80147</v>
@@ -5307,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5348,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5358,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5372,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,32 +5405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B40" t="n">
-        <v>80147</v>
+        <v>92346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115881</v>
       </c>
       <c r="B41" t="n">
-        <v>92332</v>
+        <v>80147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>530093</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179801</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,32 +5786,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6508,7 +6508,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115895</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
         <v>80147</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530122</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179836</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115899</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
         <v>80147</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530013</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179829</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,10 +6762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115930</v>
+        <v>129115899</v>
       </c>
       <c r="B51" t="n">
-        <v>91560</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6773,21 +6773,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530065</v>
+        <v>530013</v>
       </c>
       <c r="R51" t="n">
-        <v>7179830</v>
+        <v>7179829</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115912</v>
+        <v>129115895</v>
       </c>
       <c r="B52" t="n">
         <v>80147</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530071</v>
+        <v>530122</v>
       </c>
       <c r="R52" t="n">
-        <v>7179681</v>
+        <v>7179836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7016,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115878</v>
+        <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>91558</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,21 +7027,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7051,10 +7051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529899</v>
+        <v>530065</v>
       </c>
       <c r="R53" t="n">
-        <v>7179626</v>
+        <v>7179830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>80147</v>
+        <v>91536</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R56" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
         <v>80147</v>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7651,10 +7651,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>91538</v>
+        <v>80147</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7662,21 +7662,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7686,10 +7686,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7750,17 +7750,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8145,7 +8145,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91903</v>
+        <v>91912</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115864</v>
+        <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,39 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530219</v>
+        <v>530065</v>
       </c>
       <c r="R8" t="n">
-        <v>7179873</v>
+        <v>7179640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1513,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,7 +1544,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115907</v>
       </c>
       <c r="B9" t="n">
         <v>80147</v>
@@ -1569,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>530117</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1661,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115907</v>
+        <v>129115864</v>
       </c>
       <c r="B10" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,34 +1682,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530117</v>
+        <v>530219</v>
       </c>
       <c r="R10" t="n">
-        <v>7179681</v>
+        <v>7179873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,21 +1772,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,45 +1788,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>92257</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,21 +1889,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1915,50 +1905,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2403,7 +2403,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129115902</v>
+        <v>129115890</v>
       </c>
       <c r="B16" t="n">
         <v>80147</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530104</v>
+        <v>529965</v>
       </c>
       <c r="R16" t="n">
-        <v>7179773</v>
+        <v>7179650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115890</v>
+        <v>129115902</v>
       </c>
       <c r="B17" t="n">
         <v>80147</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529965</v>
+        <v>530104</v>
       </c>
       <c r="R17" t="n">
-        <v>7179650</v>
+        <v>7179773</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,7 +3282,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B23" t="n">
         <v>80147</v>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,34 +3420,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530122</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,21 +3510,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115892</v>
+        <v>129115918</v>
       </c>
       <c r="B27" t="n">
         <v>80147</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530133</v>
+        <v>529944</v>
       </c>
       <c r="R27" t="n">
-        <v>7179885</v>
+        <v>7179679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115918</v>
+        <v>129115892</v>
       </c>
       <c r="B28" t="n">
         <v>80147</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529944</v>
+        <v>530133</v>
       </c>
       <c r="R28" t="n">
-        <v>7179679</v>
+        <v>7179885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115925</v>
       </c>
       <c r="B29" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>529940</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115883</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>80181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>529906</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,7 +4288,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115901</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
         <v>80147</v>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>530042</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179851</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4415,7 +4415,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115891</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
         <v>80147</v>
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529983</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4542,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80147</v>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5147,32 +5147,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80147</v>
+        <v>92347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5405,32 +5405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115926</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
-        <v>92346</v>
+        <v>80147</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530129</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179716</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,12 +5485,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
         <v>80147</v>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>80147</v>
+        <v>91560</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,23 +6519,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6543,10 +6539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>530065</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6574,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6584,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6603,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6635,7 +6631,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115912</v>
       </c>
       <c r="B50" t="n">
         <v>80147</v>
@@ -6670,10 +6666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530071</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6701,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6711,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,7 +6758,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115899</v>
+        <v>129115878</v>
       </c>
       <c r="B51" t="n">
         <v>80147</v>
@@ -6797,10 +6793,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530013</v>
+        <v>529899</v>
       </c>
       <c r="R51" t="n">
-        <v>7179829</v>
+        <v>7179626</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6828,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6838,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7016,10 +7012,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115930</v>
+        <v>129115899</v>
       </c>
       <c r="B53" t="n">
-        <v>91558</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,21 +7023,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7051,10 +7047,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530065</v>
+        <v>530013</v>
       </c>
       <c r="R53" t="n">
-        <v>7179830</v>
+        <v>7179829</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7086,7 +7082,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7096,12 +7092,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7115,17 +7111,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7778,10 +7774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B59" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7789,34 +7785,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R59" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7848,7 +7849,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7858,12 +7859,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7874,21 +7875,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7905,10 +7891,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7916,39 +7902,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R60" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7980,7 +7961,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7990,12 +7971,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8006,6 +7987,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8142,45 +8138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B62" t="n">
-        <v>91912</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R62" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8212,7 +8216,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8222,12 +8226,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8236,7 +8240,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8255,53 +8258,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91913</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R63" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8333,7 +8328,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8343,12 +8338,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8357,6 +8352,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92258</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2403,7 +2403,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129115890</v>
+        <v>129115902</v>
       </c>
       <c r="B16" t="n">
         <v>80147</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529965</v>
+        <v>530104</v>
       </c>
       <c r="R16" t="n">
-        <v>7179650</v>
+        <v>7179773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115902</v>
+        <v>129115890</v>
       </c>
       <c r="B17" t="n">
         <v>80147</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530104</v>
+        <v>529965</v>
       </c>
       <c r="R17" t="n">
-        <v>7179773</v>
+        <v>7179650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115883</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>529906</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115925</v>
       </c>
       <c r="B26" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>529940</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115918</v>
+        <v>129115886</v>
       </c>
       <c r="B27" t="n">
         <v>80147</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529944</v>
+        <v>529943</v>
       </c>
       <c r="R27" t="n">
-        <v>7179679</v>
+        <v>7179577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115892</v>
+        <v>129115921</v>
       </c>
       <c r="B28" t="n">
         <v>80147</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530133</v>
+        <v>529933</v>
       </c>
       <c r="R28" t="n">
-        <v>7179885</v>
+        <v>7179634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,10 +4034,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115925</v>
+        <v>129115918</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4045,21 +4045,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529940</v>
+        <v>529944</v>
       </c>
       <c r="R29" t="n">
-        <v>7179623</v>
+        <v>7179679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115883</v>
+        <v>129115892</v>
       </c>
       <c r="B30" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529906</v>
+        <v>530133</v>
       </c>
       <c r="R30" t="n">
-        <v>7179662</v>
+        <v>7179885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115859</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,34 +4416,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>530097</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4480,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,12 +4490,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4511,21 +4506,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4542,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80147</v>
@@ -4577,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4660,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530042</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4745,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4787,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529983</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4846,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4856,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>91560</v>
+        <v>80147</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,19 +6519,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6539,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6574,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6584,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6603,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6631,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115912</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
         <v>80147</v>
@@ -6666,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530071</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179681</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6701,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6711,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6758,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115878</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
         <v>80147</v>
@@ -6793,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529899</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179626</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6828,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6838,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6885,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115895</v>
+        <v>129115899</v>
       </c>
       <c r="B52" t="n">
         <v>80147</v>
@@ -6920,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530122</v>
+        <v>530013</v>
       </c>
       <c r="R52" t="n">
-        <v>7179836</v>
+        <v>7179829</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6955,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6965,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7012,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115899</v>
+        <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>91560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7023,23 +7027,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530013</v>
+        <v>530065</v>
       </c>
       <c r="R53" t="n">
-        <v>7179829</v>
+        <v>7179830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7785,39 +7785,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R59" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7849,7 +7844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7859,12 +7854,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7875,6 +7870,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7891,10 +7901,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B60" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7902,34 +7912,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R60" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7961,7 +7976,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7971,12 +7986,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7987,21 +8002,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8138,53 +8138,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91913</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8216,7 +8208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8226,12 +8218,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8240,6 +8232,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8258,45 +8251,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>91913</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8328,7 +8329,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8338,12 +8339,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8352,7 +8353,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129115907</v>
       </c>
       <c r="B9" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1788,45 +1788,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>92258</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,21 +1889,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1915,50 +1905,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2035,7 +2035,7 @@
         <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129115913</v>
       </c>
       <c r="B14" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129115890</v>
       </c>
       <c r="B17" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>129115910</v>
       </c>
       <c r="B18" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>80183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,10 +3272,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115883</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529906</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179662</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115918</v>
       </c>
       <c r="B27" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>529944</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115892</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>530133</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,10 +4034,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115918</v>
+        <v>129115925</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>80148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4045,21 +4045,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529944</v>
+        <v>529940</v>
       </c>
       <c r="R29" t="n">
-        <v>7179679</v>
+        <v>7179623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115892</v>
+        <v>129115883</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>80183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530133</v>
+        <v>529906</v>
       </c>
       <c r="R30" t="n">
-        <v>7179885</v>
+        <v>7179662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4525,7 +4525,7 @@
         <v>129115922</v>
       </c>
       <c r="B33" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>129115885</v>
       </c>
       <c r="B36" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5147,45 +5147,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>92347</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5230,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5241,22 +5244,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,10 +5278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80147</v>
+        <v>92350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5662,7 +5662,7 @@
         <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>129115888</v>
       </c>
       <c r="B48" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>129115878</v>
       </c>
       <c r="B50" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>129115895</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>129115899</v>
       </c>
       <c r="B52" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>129115887</v>
       </c>
       <c r="B54" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>129115896</v>
       </c>
       <c r="B55" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115927</v>
+        <v>129115884</v>
       </c>
       <c r="B56" t="n">
-        <v>91536</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530130</v>
+        <v>529906</v>
       </c>
       <c r="R56" t="n">
-        <v>7179707</v>
+        <v>7179662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115908</v>
       </c>
       <c r="B57" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530106</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115927</v>
       </c>
       <c r="B58" t="n">
-        <v>80147</v>
+        <v>91539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>530130</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7777,7 +7777,7 @@
         <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115905</v>
       </c>
       <c r="B5" t="n">
         <v>80149</v>
@@ -1091,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530120</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115923</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>529957</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179580</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1269,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92261</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,7 +3282,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B23" t="n">
         <v>80149</v>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,34 +3420,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530122</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,21 +3510,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -5147,48 +5147,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>92350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5244,23 +5241,22 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5532,45 +5528,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B41" t="n">
-        <v>92350</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5601,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5611,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5626,22 +5625,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80183</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,45 +5786,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,10 +5903,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5924,39 +5914,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80183</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115905</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530120</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179702</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115923</v>
+        <v>129115905</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529957</v>
+        <v>530120</v>
       </c>
       <c r="R6" t="n">
-        <v>7179580</v>
+        <v>7179702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,21 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1671,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115864</v>
+        <v>129115907</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,39 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530219</v>
+        <v>530117</v>
       </c>
       <c r="R10" t="n">
-        <v>7179873</v>
+        <v>7179681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,6 +1757,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,7 +1791,7 @@
         <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,34 +2043,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,21 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2159,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2406,7 +2406,7 @@
         <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>129115890</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>129115910</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>129115879</v>
       </c>
       <c r="B20" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>129115920</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,10 +3272,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3529,7 +3529,7 @@
         <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>129115918</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>129115892</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115925</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80148</v>
+        <v>80184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529940</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179623</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115883</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80183</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529906</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179662</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115859</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,39 +4426,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530097</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179880</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4490,12 +4495,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4506,6 +4511,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,10 +4542,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4557,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115901</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4660,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530042</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4745,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115891</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4797,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529983</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,12 +4871,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>129115885</v>
       </c>
       <c r="B36" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>92350</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5303,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5344,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5354,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5368,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5401,10 +5405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5436,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5481,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5528,10 +5532,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115893</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5557,19 +5561,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530230</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179884</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5601,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5611,7 +5612,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5625,7 +5626,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80183</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5903,32 +5903,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6384,7 +6384,7 @@
         <v>129115888</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115878</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>529899</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179626</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6635,10 +6635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115895</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530122</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,10 +6762,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115899</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>530013</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179829</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6889,10 +6889,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115899</v>
+        <v>129115912</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530013</v>
+        <v>530071</v>
       </c>
       <c r="R52" t="n">
-        <v>7179829</v>
+        <v>7179681</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115887</v>
+        <v>129115896</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529887</v>
+        <v>530106</v>
       </c>
       <c r="R54" t="n">
-        <v>7179641</v>
+        <v>7179857</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7266,10 +7266,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129115896</v>
+        <v>129115887</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>530106</v>
+        <v>529887</v>
       </c>
       <c r="R55" t="n">
-        <v>7179857</v>
+        <v>7179641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>91541</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R56" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>91539</v>
+        <v>80150</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7777,7 +7777,7 @@
         <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91916</v>
+        <v>91918</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1386,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115864</v>
+        <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,39 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530219</v>
+        <v>530065</v>
       </c>
       <c r="R8" t="n">
-        <v>7179873</v>
+        <v>7179640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1513,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,10 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,34 +1555,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,21 +1645,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1791,7 +1791,7 @@
         <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +2043,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,12 +2112,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,6 +2128,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2149,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129115902</v>
+        <v>129115871</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,34 +2414,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530104</v>
+        <v>530010</v>
       </c>
       <c r="R16" t="n">
-        <v>7179773</v>
+        <v>7179829</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2478,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,12 +2488,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Synobs födosökande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,21 +2504,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2530,7 +2520,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115890</v>
+        <v>129115902</v>
       </c>
       <c r="B17" t="n">
         <v>80150</v>
@@ -2565,10 +2555,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529965</v>
+        <v>530104</v>
       </c>
       <c r="R17" t="n">
-        <v>7179650</v>
+        <v>7179773</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2590,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2600,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2657,7 +2647,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129115910</v>
+        <v>129115890</v>
       </c>
       <c r="B18" t="n">
         <v>80150</v>
@@ -2692,10 +2682,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530085</v>
+        <v>529965</v>
       </c>
       <c r="R18" t="n">
-        <v>7179685</v>
+        <v>7179650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2727,7 +2717,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2727,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2784,10 +2774,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129115871</v>
+        <v>129115910</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2795,39 +2785,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530010</v>
+        <v>530085</v>
       </c>
       <c r="R19" t="n">
-        <v>7179829</v>
+        <v>7179685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2859,7 +2844,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2869,12 +2854,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Synobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,6 +2870,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115859</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,34 +4416,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>530097</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4480,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,12 +4490,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4511,21 +4506,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4542,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4577,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4660,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530042</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4745,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4787,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529983</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4846,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4856,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5150,7 +5150,7 @@
         <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>92352</v>
+        <v>92356</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5786,50 +5786,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,45 +5913,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,7 +6508,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115878</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
         <v>80150</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529899</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179626</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6635,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115895</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
         <v>80150</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530122</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179836</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115899</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
         <v>80150</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530013</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179829</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6889,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115912</v>
+        <v>129115899</v>
       </c>
       <c r="B52" t="n">
         <v>80150</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530071</v>
+        <v>530013</v>
       </c>
       <c r="R52" t="n">
-        <v>7179681</v>
+        <v>7179829</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115896</v>
+        <v>129115887</v>
       </c>
       <c r="B54" t="n">
         <v>80150</v>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>530106</v>
+        <v>529887</v>
       </c>
       <c r="R54" t="n">
-        <v>7179857</v>
+        <v>7179641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7266,7 +7266,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129115887</v>
+        <v>129115896</v>
       </c>
       <c r="B55" t="n">
         <v>80150</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529887</v>
+        <v>530106</v>
       </c>
       <c r="R55" t="n">
-        <v>7179641</v>
+        <v>7179857</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7396,7 +7396,7 @@
         <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91918</v>
+        <v>91922</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1152,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1311,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,21 +1401,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,21 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,10 +1534,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115864</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,39 +1545,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530219</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179873</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,12 +1614,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,6 +1630,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1788,45 +1788,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>92267</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,21 +1889,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1915,50 +1905,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,34 +2043,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,21 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2159,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115859</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,39 +4426,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530097</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179880</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4490,12 +4495,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4506,6 +4511,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4557,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115901</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4660,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530042</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4745,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115891</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4797,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529983</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,12 +4871,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5147,45 +5147,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>92356</v>
+        <v>80150</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5230,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5241,22 +5244,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,7 +5278,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
         <v>80150</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>92357</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5670,34 +5670,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5734,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5744,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5755,21 +5760,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5913,10 +5903,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5924,39 +5914,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115927</v>
+        <v>129115884</v>
       </c>
       <c r="B56" t="n">
-        <v>91545</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530130</v>
+        <v>529906</v>
       </c>
       <c r="R56" t="n">
-        <v>7179707</v>
+        <v>7179662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115908</v>
       </c>
       <c r="B57" t="n">
         <v>80150</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530106</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115927</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>530130</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8138,45 +8138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B62" t="n">
-        <v>91922</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R62" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8208,7 +8216,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8218,12 +8226,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8232,7 +8240,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8251,53 +8258,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91923</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R63" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8329,7 +8328,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8339,12 +8338,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8353,6 +8352,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115883</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>529906</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115925</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>529940</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115918</v>
+        <v>129115886</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529944</v>
+        <v>529943</v>
       </c>
       <c r="R27" t="n">
-        <v>7179679</v>
+        <v>7179577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115892</v>
+        <v>129115921</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530133</v>
+        <v>529933</v>
       </c>
       <c r="R28" t="n">
-        <v>7179885</v>
+        <v>7179634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115918</v>
       </c>
       <c r="B29" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>529944</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115892</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>530133</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115859</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,34 +4416,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>530097</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4480,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,12 +4490,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4511,21 +4506,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4542,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4577,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4660,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530042</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4745,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4787,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529983</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4846,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4856,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5147,48 +5147,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80150</v>
+        <v>92357</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5244,23 +5241,22 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5278,7 +5274,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5307,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5348,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5358,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5372,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
         <v>80150</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
-        <v>92357</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,50 +5659,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5734,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5744,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,6 +5755,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5776,45 +5786,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5846,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5856,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5872,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -8138,53 +8138,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91923</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8216,7 +8208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8226,12 +8218,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8240,6 +8232,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8258,45 +8251,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>91923</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8328,7 +8329,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8338,12 +8339,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8352,7 +8353,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +2043,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,12 +2112,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,6 +2128,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2149,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,7 +3282,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B23" t="n">
         <v>80150</v>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,34 +3420,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530122</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,21 +3510,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115883</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529906</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179662</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115918</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>529944</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115892</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>530133</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115918</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529944</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179679</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115859</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,39 +4426,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530097</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179880</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4490,12 +4495,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4506,6 +4511,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4557,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115901</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4660,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530042</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4745,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115891</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4797,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529983</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,12 +4871,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R56" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
         <v>80150</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>91546</v>
+        <v>80150</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115864</v>
+        <v>129115915</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,39 +1428,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530219</v>
+        <v>530065</v>
       </c>
       <c r="R8" t="n">
-        <v>7179873</v>
+        <v>7179640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1513,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,7 +1544,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115907</v>
       </c>
       <c r="B9" t="n">
         <v>80150</v>
@@ -1569,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>530117</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1661,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115907</v>
+        <v>129115864</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,34 +1682,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530117</v>
+        <v>530219</v>
       </c>
       <c r="R10" t="n">
-        <v>7179681</v>
+        <v>7179873</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,12 +1756,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,21 +1772,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92268</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2403,10 +2403,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129115871</v>
+        <v>129115902</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,39 +2414,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530010</v>
+        <v>530104</v>
       </c>
       <c r="R16" t="n">
-        <v>7179829</v>
+        <v>7179773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2478,7 +2473,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2488,12 +2483,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Synobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,6 +2499,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2520,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115902</v>
+        <v>129115890</v>
       </c>
       <c r="B17" t="n">
         <v>80150</v>
@@ -2555,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530104</v>
+        <v>529965</v>
       </c>
       <c r="R17" t="n">
-        <v>7179773</v>
+        <v>7179650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2590,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2600,7 +2610,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2647,7 +2657,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129115890</v>
+        <v>129115910</v>
       </c>
       <c r="B18" t="n">
         <v>80150</v>
@@ -2682,10 +2692,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529965</v>
+        <v>530085</v>
       </c>
       <c r="R18" t="n">
-        <v>7179650</v>
+        <v>7179685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2717,7 +2727,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2727,7 +2737,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2774,10 +2784,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129115910</v>
+        <v>129115871</v>
       </c>
       <c r="B19" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2785,34 +2795,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530085</v>
+        <v>530010</v>
       </c>
       <c r="R19" t="n">
-        <v>7179685</v>
+        <v>7179829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2844,7 +2859,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2854,12 +2869,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Synobs födosökande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2870,21 +2885,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2901,32 +2901,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115879</v>
+        <v>129115920</v>
       </c>
       <c r="B20" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530093</v>
+        <v>529936</v>
       </c>
       <c r="R20" t="n">
-        <v>7179801</v>
+        <v>7179647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3028,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115920</v>
+        <v>129115879</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529936</v>
+        <v>530093</v>
       </c>
       <c r="R21" t="n">
-        <v>7179647</v>
+        <v>7179801</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3526,7 +3526,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115918</v>
       </c>
       <c r="B25" t="n">
         <v>80150</v>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>529944</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179679</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,7 +3653,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115892</v>
       </c>
       <c r="B26" t="n">
         <v>80150</v>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>530133</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115918</v>
+        <v>129115886</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529944</v>
+        <v>529943</v>
       </c>
       <c r="R27" t="n">
-        <v>7179679</v>
+        <v>7179577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115892</v>
+        <v>129115921</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530133</v>
+        <v>529933</v>
       </c>
       <c r="R28" t="n">
-        <v>7179885</v>
+        <v>7179634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,10 +4405,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115859</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,34 +4416,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>530097</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179880</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4480,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,12 +4490,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4511,21 +4506,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4542,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115922</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4577,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115901</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4660,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>530042</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4729,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4745,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4776,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115891</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4787,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529983</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4846,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4856,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4872,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5147,45 +5147,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>92357</v>
+        <v>80150</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5230,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5241,22 +5244,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,7 +5278,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
         <v>80150</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>92360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,50 +5786,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,10 +5913,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5914,34 +5924,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -7019,7 +7019,7 @@
         <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91923</v>
+        <v>91926</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +940,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1030,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1259,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1370,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1386,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,34 +2043,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,21 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2159,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115890</v>
+        <v>129115910</v>
       </c>
       <c r="B17" t="n">
         <v>80150</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529965</v>
+        <v>530085</v>
       </c>
       <c r="R17" t="n">
-        <v>7179650</v>
+        <v>7179685</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129115910</v>
+        <v>129115890</v>
       </c>
       <c r="B18" t="n">
         <v>80150</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530085</v>
+        <v>529965</v>
       </c>
       <c r="R18" t="n">
-        <v>7179685</v>
+        <v>7179650</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,7 +3272,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
         <v>80150</v>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,7 +3526,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115918</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
         <v>80150</v>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529944</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179679</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,7 +3653,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115892</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
         <v>80150</v>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>530133</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179885</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115892</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>530133</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115925</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>529940</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179623</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115918</v>
       </c>
       <c r="B29" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>529944</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115883</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>529906</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4522,7 +4522,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115922</v>
+        <v>129115901</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529936</v>
+        <v>530042</v>
       </c>
       <c r="R33" t="n">
-        <v>7179603</v>
+        <v>7179851</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,7 +4649,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115901</v>
+        <v>129115922</v>
       </c>
       <c r="B34" t="n">
         <v>80150</v>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>530042</v>
+        <v>529936</v>
       </c>
       <c r="R34" t="n">
-        <v>7179851</v>
+        <v>7179603</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115924</v>
       </c>
       <c r="B38" t="n">
         <v>80150</v>
@@ -5176,19 +5176,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>529939</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179590</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,7 +5227,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5244,7 +5241,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5405,32 +5401,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>92360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5440,10 +5436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5471,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,12 +5481,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,17 +5500,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5532,45 +5528,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B41" t="n">
-        <v>92360</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5601,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5611,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5626,22 +5625,23 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,45 +5786,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,10 +5903,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5924,39 +5914,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6762,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115899</v>
       </c>
       <c r="B51" t="n">
         <v>80150</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>530013</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179829</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6889,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115899</v>
+        <v>129115895</v>
       </c>
       <c r="B52" t="n">
         <v>80150</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530013</v>
+        <v>530122</v>
       </c>
       <c r="R52" t="n">
-        <v>7179829</v>
+        <v>7179836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B56" t="n">
-        <v>91549</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R56" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115927</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>91549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>530130</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7785,34 +7785,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R59" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7844,7 +7849,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7854,12 +7859,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7870,21 +7875,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7901,10 +7891,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7912,39 +7902,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R60" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7976,7 +7961,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7986,12 +7971,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8002,6 +7987,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115877</v>
+        <v>129115900</v>
       </c>
       <c r="B2" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529899</v>
+        <v>530026</v>
       </c>
       <c r="R2" t="n">
-        <v>7179626</v>
+        <v>7179833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115900</v>
+        <v>129115877</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530026</v>
+        <v>529899</v>
       </c>
       <c r="R3" t="n">
-        <v>7179833</v>
+        <v>7179626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115876</v>
+        <v>129115905</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530020</v>
+        <v>530120</v>
       </c>
       <c r="R4" t="n">
-        <v>7179835</v>
+        <v>7179702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1046,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115868</v>
+        <v>129115923</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,39 +1067,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530106</v>
+        <v>529957</v>
       </c>
       <c r="R5" t="n">
-        <v>7179856</v>
+        <v>7179580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1152,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115905</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530120</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179702</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1284,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115923</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1311,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529957</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179580</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,21 +1401,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +2043,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,12 +2112,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,6 +2128,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2149,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2530,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115910</v>
+        <v>129115890</v>
       </c>
       <c r="B17" t="n">
         <v>80150</v>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530085</v>
+        <v>529965</v>
       </c>
       <c r="R17" t="n">
-        <v>7179685</v>
+        <v>7179650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129115890</v>
+        <v>129115910</v>
       </c>
       <c r="B18" t="n">
         <v>80150</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529965</v>
+        <v>530085</v>
       </c>
       <c r="R18" t="n">
-        <v>7179650</v>
+        <v>7179685</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,7 +3282,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B23" t="n">
         <v>80150</v>
@@ -3307,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,10 +3409,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115866</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3410,34 +3420,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530122</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3484,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3494,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3495,21 +3510,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115883</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>529906</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115925</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>529940</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179623</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115892</v>
+        <v>129115886</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>530133</v>
+        <v>529943</v>
       </c>
       <c r="R27" t="n">
-        <v>7179885</v>
+        <v>7179577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3907,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R28" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4161,32 +4161,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115883</v>
+        <v>129115892</v>
       </c>
       <c r="B30" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529906</v>
+        <v>530133</v>
       </c>
       <c r="R30" t="n">
-        <v>7179662</v>
+        <v>7179885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,10 +4415,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115859</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,39 +4426,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530097</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179880</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4480,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4490,12 +4495,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4506,6 +4511,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4522,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115901</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4557,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530042</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4592,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4649,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4660,34 +4680,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4745,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4776,10 +4786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115891</v>
+        <v>129115859</v>
       </c>
       <c r="B35" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4787,34 +4797,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529983</v>
+        <v>530097</v>
       </c>
       <c r="R35" t="n">
-        <v>7179662</v>
+        <v>7179880</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,7 +4861,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4856,12 +4871,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4872,21 +4887,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5147,32 +5147,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80150</v>
+        <v>92360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5303,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5344,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5354,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5368,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5401,32 +5405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115926</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
-        <v>92360</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5436,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530129</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179716</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5471,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5481,12 +5485,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5500,17 +5504,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5528,7 +5532,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115893</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
         <v>80150</v>
@@ -5557,19 +5561,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530230</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179884</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5601,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5611,7 +5612,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5625,7 +5626,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5786,10 +5786,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5797,39 +5797,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,10 +5913,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5914,34 +5924,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6762,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115899</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
         <v>80150</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530013</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179829</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6889,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115895</v>
+        <v>129115899</v>
       </c>
       <c r="B52" t="n">
         <v>80150</v>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530122</v>
+        <v>530013</v>
       </c>
       <c r="R52" t="n">
-        <v>7179836</v>
+        <v>7179829</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7393,7 +7393,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B56" t="n">
         <v>80150</v>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R56" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7520,7 +7520,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115908</v>
       </c>
       <c r="B57" t="n">
         <v>80150</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530106</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179677</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7774,10 +7774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115867</v>
+        <v>129115919</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7785,39 +7785,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>530121</v>
+        <v>529917</v>
       </c>
       <c r="R59" t="n">
-        <v>7179847</v>
+        <v>7179686</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7849,7 +7844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7859,12 +7854,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7875,6 +7870,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7891,10 +7901,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115919</v>
+        <v>129115867</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7902,34 +7912,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529917</v>
+        <v>530121</v>
       </c>
       <c r="R60" t="n">
-        <v>7179686</v>
+        <v>7179847</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7961,7 +7976,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7971,12 +7986,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7987,21 +8002,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115856</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,34 +4299,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529991</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4363,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,12 +4373,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4384,21 +4389,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4415,7 +4405,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115922</v>
       </c>
       <c r="B32" t="n">
         <v>80150</v>
@@ -4450,10 +4440,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>529936</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179603</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4475,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,7 +4485,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4542,7 +4532,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115901</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4577,10 +4567,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>530042</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179851</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4602,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4612,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4659,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115891</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,36 +4670,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>529983</v>
       </c>
       <c r="R34" t="n">
         <v>7179662</v>
@@ -4744,7 +4729,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4739,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4755,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5147,45 +5147,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115893</v>
       </c>
       <c r="B38" t="n">
-        <v>92360</v>
+        <v>80150</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>530230</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5220,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5230,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5241,22 +5244,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,7 +5278,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115881</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5303,19 +5307,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>530093</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179801</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5348,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5358,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5372,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115924</v>
       </c>
       <c r="B40" t="n">
         <v>80150</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>530093</v>
+        <v>529939</v>
       </c>
       <c r="R40" t="n">
-        <v>7179801</v>
+        <v>7179590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115926</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>92360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>530129</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179716</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115897</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>530101</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179860</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115897</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5797,34 +5797,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530101</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179860</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,50 +5903,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115930</v>
       </c>
       <c r="B49" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,23 +6519,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6543,10 +6539,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>530065</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179830</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6574,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6584,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,17 +6603,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6635,7 +6631,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115912</v>
       </c>
       <c r="B50" t="n">
         <v>80150</v>
@@ -6670,10 +6666,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530071</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6701,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,7 +6711,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6762,7 +6758,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115878</v>
       </c>
       <c r="B51" t="n">
         <v>80150</v>
@@ -6797,10 +6793,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>529899</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179626</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6828,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,7 +6838,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6889,7 +6885,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115899</v>
+        <v>129115895</v>
       </c>
       <c r="B52" t="n">
         <v>80150</v>
@@ -6924,10 +6920,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530013</v>
+        <v>530122</v>
       </c>
       <c r="R52" t="n">
-        <v>7179829</v>
+        <v>7179836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6955,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,7 +6965,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7016,10 +7012,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115930</v>
+        <v>129115899</v>
       </c>
       <c r="B53" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,19 +7023,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530065</v>
+        <v>530013</v>
       </c>
       <c r="R53" t="n">
-        <v>7179830</v>
+        <v>7179829</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115868</v>
+        <v>129115876</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530106</v>
+        <v>530020</v>
       </c>
       <c r="R6" t="n">
-        <v>7179856</v>
+        <v>7179835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115876</v>
+        <v>129115868</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530020</v>
+        <v>530106</v>
       </c>
       <c r="R7" t="n">
-        <v>7179835</v>
+        <v>7179856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115915</v>
+        <v>129115864</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,34 +1428,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530065</v>
+        <v>530219</v>
       </c>
       <c r="R8" t="n">
-        <v>7179640</v>
+        <v>7179873</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,21 +1518,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1544,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115907</v>
+        <v>129115915</v>
       </c>
       <c r="B9" t="n">
         <v>80150</v>
@@ -1579,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530117</v>
+        <v>530065</v>
       </c>
       <c r="R9" t="n">
-        <v>7179681</v>
+        <v>7179640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1671,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115864</v>
+        <v>129115907</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,39 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530219</v>
+        <v>530117</v>
       </c>
       <c r="R10" t="n">
-        <v>7179873</v>
+        <v>7179681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,12 +1741,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,6 +1757,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,45 +1788,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,21 +1889,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1915,50 +1905,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115869</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,34 +2043,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530007</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,21 +2133,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2159,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115898</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2194,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530060</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115913</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2287,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530075</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2356,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2372,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3240,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,21 +3256,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3282,7 +3272,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115903</v>
+        <v>129115916</v>
       </c>
       <c r="B23" t="n">
         <v>80150</v>
@@ -3317,10 +3307,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530123</v>
+        <v>530018</v>
       </c>
       <c r="R23" t="n">
-        <v>7179756</v>
+        <v>7179628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3342,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3352,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,10 +3399,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115866</v>
+        <v>129115903</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,39 +3410,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530122</v>
+        <v>530123</v>
       </c>
       <c r="R24" t="n">
-        <v>7179838</v>
+        <v>7179756</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3484,7 +3469,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3494,12 +3479,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,6 +3495,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3526,32 +3526,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115883</v>
+        <v>129115886</v>
       </c>
       <c r="B25" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529906</v>
+        <v>529943</v>
       </c>
       <c r="R25" t="n">
-        <v>7179662</v>
+        <v>7179577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115925</v>
+        <v>129115921</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529940</v>
+        <v>529933</v>
       </c>
       <c r="R26" t="n">
-        <v>7179623</v>
+        <v>7179634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115886</v>
+        <v>129115918</v>
       </c>
       <c r="B27" t="n">
         <v>80150</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529943</v>
+        <v>529944</v>
       </c>
       <c r="R27" t="n">
-        <v>7179577</v>
+        <v>7179679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,7 +3907,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115921</v>
+        <v>129115892</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529933</v>
+        <v>530133</v>
       </c>
       <c r="R28" t="n">
-        <v>7179634</v>
+        <v>7179885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4034,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115918</v>
+        <v>129115883</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529944</v>
+        <v>529906</v>
       </c>
       <c r="R29" t="n">
-        <v>7179679</v>
+        <v>7179662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4161,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115892</v>
+        <v>129115925</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>530133</v>
+        <v>529940</v>
       </c>
       <c r="R30" t="n">
-        <v>7179885</v>
+        <v>7179623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115856</v>
+        <v>129115922</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4299,39 +4299,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529991</v>
+        <v>529936</v>
       </c>
       <c r="R31" t="n">
-        <v>7179662</v>
+        <v>7179603</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4358,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4373,12 +4368,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4389,6 +4384,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4405,7 +4415,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115922</v>
+        <v>129115901</v>
       </c>
       <c r="B32" t="n">
         <v>80150</v>
@@ -4440,10 +4450,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529936</v>
+        <v>530042</v>
       </c>
       <c r="R32" t="n">
-        <v>7179603</v>
+        <v>7179851</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4475,7 +4485,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4485,7 +4495,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4532,7 +4542,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115901</v>
+        <v>129115891</v>
       </c>
       <c r="B33" t="n">
         <v>80150</v>
@@ -4567,10 +4577,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>530042</v>
+        <v>529983</v>
       </c>
       <c r="R33" t="n">
-        <v>7179851</v>
+        <v>7179662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4602,7 +4612,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4612,7 +4622,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4659,10 +4669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115891</v>
+        <v>129115856</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4670,31 +4680,36 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529983</v>
+        <v>529991</v>
       </c>
       <c r="R34" t="n">
         <v>7179662</v>
@@ -4729,7 +4744,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4739,12 +4754,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4755,21 +4770,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -5147,48 +5147,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115893</v>
+        <v>129115926</v>
       </c>
       <c r="B38" t="n">
-        <v>80150</v>
+        <v>92360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530230</v>
+        <v>530129</v>
       </c>
       <c r="R38" t="n">
-        <v>7179884</v>
+        <v>7179716</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5220,7 +5217,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5230,12 +5227,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5244,23 +5241,22 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5278,7 +5274,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115881</v>
+        <v>129115893</v>
       </c>
       <c r="B39" t="n">
         <v>80150</v>
@@ -5307,16 +5303,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530093</v>
+        <v>530230</v>
       </c>
       <c r="R39" t="n">
-        <v>7179801</v>
+        <v>7179884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5348,7 +5347,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5358,7 +5357,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5372,6 +5371,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,7 +5405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115924</v>
+        <v>129115881</v>
       </c>
       <c r="B40" t="n">
         <v>80150</v>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529939</v>
+        <v>530093</v>
       </c>
       <c r="R40" t="n">
-        <v>7179590</v>
+        <v>7179801</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5532,32 +5532,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115926</v>
+        <v>129115924</v>
       </c>
       <c r="B41" t="n">
-        <v>92360</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>918</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>530129</v>
+        <v>529939</v>
       </c>
       <c r="R41" t="n">
-        <v>7179716</v>
+        <v>7179590</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5786,50 +5786,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115931</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530134</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179826</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5856,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5866,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5887,6 +5882,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5903,45 +5913,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R44" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +5988,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +5998,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6014,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -7393,10 +7393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115884</v>
+        <v>129115927</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>91549</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529906</v>
+        <v>530130</v>
       </c>
       <c r="R56" t="n">
-        <v>7179662</v>
+        <v>7179707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115908</v>
+        <v>129115884</v>
       </c>
       <c r="B57" t="n">
         <v>80150</v>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R57" t="n">
-        <v>7179677</v>
+        <v>7179662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7647,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115927</v>
+        <v>129115908</v>
       </c>
       <c r="B58" t="n">
-        <v>91549</v>
+        <v>80150</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530130</v>
+        <v>530106</v>
       </c>
       <c r="R58" t="n">
-        <v>7179707</v>
+        <v>7179677</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8138,45 +8138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B62" t="n">
-        <v>91926</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R62" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8208,7 +8216,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8218,12 +8226,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8232,7 +8240,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8251,53 +8258,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91926</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R63" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8329,7 +8328,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8339,12 +8338,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8353,6 +8352,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -1788,50 +1788,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115875</v>
+        <v>129115853</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529938</v>
+        <v>530213</v>
       </c>
       <c r="R11" t="n">
-        <v>7179691</v>
+        <v>7179861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,12 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,6 +1884,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,45 +1915,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115853</v>
+        <v>129115875</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530213</v>
+        <v>529938</v>
       </c>
       <c r="R12" t="n">
-        <v>7179861</v>
+        <v>7179691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1990,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +2000,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,21 +2016,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115869</v>
+        <v>129115898</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,39 +2043,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530007</v>
+        <v>530060</v>
       </c>
       <c r="R13" t="n">
-        <v>7179831</v>
+        <v>7179882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,12 +2112,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,6 +2128,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2149,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115898</v>
+        <v>129115913</v>
       </c>
       <c r="B14" t="n">
         <v>80150</v>
@@ -2184,10 +2194,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530060</v>
+        <v>530075</v>
       </c>
       <c r="R14" t="n">
-        <v>7179882</v>
+        <v>7179670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2276,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115913</v>
+        <v>129115869</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,34 +2297,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530075</v>
+        <v>530007</v>
       </c>
       <c r="R15" t="n">
-        <v>7179670</v>
+        <v>7179831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2356,12 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,21 +2387,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115866</v>
+        <v>129115916</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3166,39 +3166,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530122</v>
+        <v>530018</v>
       </c>
       <c r="R22" t="n">
-        <v>7179838</v>
+        <v>7179628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,7 +3225,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3240,12 +3235,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,6 +3251,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3272,10 +3282,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115916</v>
+        <v>129115866</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3283,34 +3293,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530018</v>
+        <v>530122</v>
       </c>
       <c r="R23" t="n">
-        <v>7179628</v>
+        <v>7179838</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3342,7 +3357,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3352,12 +3367,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3368,21 +3383,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -5659,32 +5659,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115897</v>
+        <v>129115931</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530101</v>
+        <v>530134</v>
       </c>
       <c r="R42" t="n">
-        <v>7179860</v>
+        <v>7179826</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5786,45 +5786,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115931</v>
+        <v>129115858</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530134</v>
+        <v>530014</v>
       </c>
       <c r="R43" t="n">
-        <v>7179826</v>
+        <v>7179865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5856,7 +5861,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5866,12 +5871,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5882,21 +5887,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5913,10 +5903,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115858</v>
+        <v>129115897</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5924,39 +5914,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530014</v>
+        <v>530101</v>
       </c>
       <c r="R44" t="n">
-        <v>7179865</v>
+        <v>7179860</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5988,7 +5973,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5998,12 +5983,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6014,6 +5999,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115930</v>
+        <v>129115912</v>
       </c>
       <c r="B49" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,19 +6519,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6539,10 +6543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530065</v>
+        <v>530071</v>
       </c>
       <c r="R49" t="n">
-        <v>7179830</v>
+        <v>7179681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6574,7 +6578,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6584,12 +6588,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6603,17 +6607,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6631,7 +6635,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115912</v>
+        <v>129115878</v>
       </c>
       <c r="B50" t="n">
         <v>80150</v>
@@ -6666,10 +6670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>530071</v>
+        <v>529899</v>
       </c>
       <c r="R50" t="n">
-        <v>7179681</v>
+        <v>7179626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6701,7 +6705,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6711,7 +6715,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6758,7 +6762,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115878</v>
+        <v>129115895</v>
       </c>
       <c r="B51" t="n">
         <v>80150</v>
@@ -6793,10 +6797,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529899</v>
+        <v>530122</v>
       </c>
       <c r="R51" t="n">
-        <v>7179626</v>
+        <v>7179836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6828,7 +6832,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6838,7 +6842,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6885,7 +6889,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115895</v>
+        <v>129115899</v>
       </c>
       <c r="B52" t="n">
         <v>80150</v>
@@ -6920,10 +6924,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530122</v>
+        <v>530013</v>
       </c>
       <c r="R52" t="n">
-        <v>7179836</v>
+        <v>7179829</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6955,7 +6959,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6965,7 +6969,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7012,10 +7016,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115899</v>
+        <v>129115930</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7023,23 +7027,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530013</v>
+        <v>530065</v>
       </c>
       <c r="R53" t="n">
-        <v>7179829</v>
+        <v>7179830</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död stående gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8138,53 +8138,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91926</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8216,7 +8208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8226,12 +8218,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8240,6 +8232,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8258,45 +8251,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>91926</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8328,7 +8329,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8338,12 +8339,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8352,7 +8353,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -8021,7 +8021,7 @@
         <v>129115855</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>129115928</v>
       </c>
       <c r="B62" t="n">
-        <v>91926</v>
+        <v>91954</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>129115874</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -8021,7 +8021,7 @@
         <v>129115855</v>
       </c>
       <c r="B61" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8138,45 +8138,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115928</v>
+        <v>129115874</v>
       </c>
       <c r="B62" t="n">
-        <v>91954</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530065</v>
+        <v>530014</v>
       </c>
       <c r="R62" t="n">
-        <v>7179830</v>
+        <v>7179668</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8208,7 +8216,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8218,12 +8226,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8232,7 +8240,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8251,53 +8258,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115874</v>
+        <v>129115928</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>91960</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530014</v>
+        <v>530065</v>
       </c>
       <c r="R63" t="n">
-        <v>7179668</v>
+        <v>7179830</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8329,7 +8328,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8339,12 +8338,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8353,6 +8352,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129115900</v>
+        <v>129115926</v>
       </c>
       <c r="B2" t="n">
-        <v>80150</v>
+        <v>92721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>918</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530026</v>
+        <v>530129</v>
       </c>
       <c r="R2" t="n">
-        <v>7179833</v>
+        <v>7179716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal mossig granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,17 +774,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129115877</v>
+        <v>129115927</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529899</v>
+        <v>530130</v>
       </c>
       <c r="R3" t="n">
-        <v>7179626</v>
+        <v>7179707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På granstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,17 +901,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,32 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129115905</v>
+        <v>129115928</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>92283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530120</v>
+        <v>530065</v>
       </c>
       <c r="R4" t="n">
-        <v>7179702</v>
+        <v>7179830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,23 +1023,9 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1042,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129115923</v>
+        <v>129115878</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529957</v>
+        <v>529899</v>
       </c>
       <c r="R5" t="n">
-        <v>7179580</v>
+        <v>7179626</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129115876</v>
+        <v>129115881</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1180,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530020</v>
+        <v>530093</v>
       </c>
       <c r="R6" t="n">
-        <v>7179835</v>
+        <v>7179801</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1249,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ljudobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,6 +1265,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129115868</v>
+        <v>129115884</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,39 +1307,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530106</v>
+        <v>529906</v>
       </c>
       <c r="R7" t="n">
-        <v>7179856</v>
+        <v>7179662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,12 +1376,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobs bild födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,6 +1392,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,10 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129115864</v>
+        <v>129115886</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,39 +1434,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530219</v>
+        <v>529943</v>
       </c>
       <c r="R8" t="n">
-        <v>7179873</v>
+        <v>7179577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1503,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,6 +1519,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1534,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129115915</v>
+        <v>129115887</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,10 +1585,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530065</v>
+        <v>529887</v>
       </c>
       <c r="R9" t="n">
-        <v>7179640</v>
+        <v>7179641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1630,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1661,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129115907</v>
+        <v>129115888</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530117</v>
+        <v>529919</v>
       </c>
       <c r="R10" t="n">
-        <v>7179681</v>
+        <v>7179636</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,7 +1747,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,7 +1757,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1788,32 +1804,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129115853</v>
+        <v>129115890</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1839,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530213</v>
+        <v>529965</v>
       </c>
       <c r="R11" t="n">
-        <v>7179861</v>
+        <v>7179650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,7 +1874,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1884,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På knäckt gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,17 +1903,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1915,10 +1931,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129115875</v>
+        <v>129115891</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,39 +1942,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529938</v>
+        <v>529983</v>
       </c>
       <c r="R12" t="n">
-        <v>7179691</v>
+        <v>7179662</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,7 +2001,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2000,12 +2011,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,6 +2027,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2032,10 +2058,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129115898</v>
+        <v>129115892</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,10 +2093,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530060</v>
+        <v>530133</v>
       </c>
       <c r="R13" t="n">
-        <v>7179882</v>
+        <v>7179885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2102,7 +2128,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2138,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2159,10 +2185,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129115913</v>
+        <v>129115895</v>
       </c>
       <c r="B14" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,10 +2220,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530075</v>
+        <v>530122</v>
       </c>
       <c r="R14" t="n">
-        <v>7179670</v>
+        <v>7179836</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2255,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2265,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2286,10 +2312,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129115869</v>
+        <v>129115896</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,39 +2323,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530007</v>
+        <v>530106</v>
       </c>
       <c r="R15" t="n">
-        <v>7179831</v>
+        <v>7179857</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2361,7 +2382,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2371,12 +2392,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,6 +2408,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2403,10 +2439,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129115902</v>
+        <v>129115897</v>
       </c>
       <c r="B16" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2438,10 +2474,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530104</v>
+        <v>530101</v>
       </c>
       <c r="R16" t="n">
-        <v>7179773</v>
+        <v>7179860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2509,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,12 +2519,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,10 +2566,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129115890</v>
+        <v>129115898</v>
       </c>
       <c r="B17" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,10 +2601,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529965</v>
+        <v>530060</v>
       </c>
       <c r="R17" t="n">
-        <v>7179650</v>
+        <v>7179882</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2600,7 +2636,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2610,7 +2646,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2657,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129115910</v>
+        <v>129115899</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,10 +2728,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530085</v>
+        <v>530013</v>
       </c>
       <c r="R18" t="n">
-        <v>7179685</v>
+        <v>7179829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2727,7 +2763,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2737,7 +2773,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2784,10 +2820,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129115871</v>
+        <v>129115900</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2795,39 +2831,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530010</v>
+        <v>530026</v>
       </c>
       <c r="R19" t="n">
-        <v>7179829</v>
+        <v>7179833</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2859,7 +2890,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2869,12 +2900,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Synobs födosökande</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,6 +2916,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2901,10 +2947,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129115920</v>
+        <v>129115901</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2936,10 +2982,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529936</v>
+        <v>530042</v>
       </c>
       <c r="R20" t="n">
-        <v>7179647</v>
+        <v>7179851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2971,7 +3017,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2981,7 +3027,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3028,32 +3074,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129115879</v>
+        <v>129115902</v>
       </c>
       <c r="B21" t="n">
-        <v>80184</v>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3063,10 +3109,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530093</v>
+        <v>530104</v>
       </c>
       <c r="R21" t="n">
-        <v>7179801</v>
+        <v>7179773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3098,7 +3144,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3108,7 +3154,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3155,10 +3201,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129115916</v>
+        <v>129115903</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3190,10 +3236,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530018</v>
+        <v>530123</v>
       </c>
       <c r="R22" t="n">
-        <v>7179628</v>
+        <v>7179756</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3225,7 +3271,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3235,12 +3281,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg och gran under</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3282,10 +3328,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129115866</v>
+        <v>129115905</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,39 +3339,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530122</v>
+        <v>530120</v>
       </c>
       <c r="R23" t="n">
-        <v>7179838</v>
+        <v>7179702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3357,7 +3398,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3367,12 +3408,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3383,6 +3424,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3399,10 +3455,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129115903</v>
+        <v>129115907</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3434,10 +3490,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530123</v>
+        <v>530117</v>
       </c>
       <c r="R24" t="n">
-        <v>7179756</v>
+        <v>7179681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3525,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3535,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På levande sälg och gran under</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3526,10 +3582,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129115886</v>
+        <v>129115908</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3561,10 +3617,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529943</v>
+        <v>530106</v>
       </c>
       <c r="R25" t="n">
-        <v>7179577</v>
+        <v>7179677</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,7 +3652,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3606,7 +3662,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3653,10 +3709,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129115921</v>
+        <v>129115910</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,10 +3744,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529933</v>
+        <v>530085</v>
       </c>
       <c r="R26" t="n">
-        <v>7179634</v>
+        <v>7179685</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3723,7 +3779,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3733,7 +3789,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3780,10 +3836,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129115918</v>
+        <v>129115912</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,10 +3871,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529944</v>
+        <v>530071</v>
       </c>
       <c r="R27" t="n">
-        <v>7179679</v>
+        <v>7179681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3850,7 +3906,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3860,7 +3916,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3907,10 +3963,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129115892</v>
+        <v>129115913</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3942,10 +3998,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>530133</v>
+        <v>530075</v>
       </c>
       <c r="R28" t="n">
-        <v>7179885</v>
+        <v>7179670</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3977,7 +4033,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3987,7 +4043,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4034,32 +4090,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129115883</v>
+        <v>129115915</v>
       </c>
       <c r="B29" t="n">
-        <v>80184</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4069,10 +4125,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529906</v>
+        <v>530065</v>
       </c>
       <c r="R29" t="n">
-        <v>7179662</v>
+        <v>7179640</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4104,7 +4160,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4114,7 +4170,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4161,10 +4217,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129115925</v>
+        <v>129115916</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4172,21 +4228,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4196,10 +4252,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529940</v>
+        <v>530018</v>
       </c>
       <c r="R30" t="n">
-        <v>7179623</v>
+        <v>7179628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4231,7 +4287,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4241,12 +4297,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4288,10 +4344,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129115922</v>
+        <v>129115918</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4323,10 +4379,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529936</v>
+        <v>529944</v>
       </c>
       <c r="R31" t="n">
-        <v>7179603</v>
+        <v>7179679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4358,7 +4414,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,7 +4424,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4415,10 +4471,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129115901</v>
+        <v>129115919</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4450,10 +4506,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>530042</v>
+        <v>529917</v>
       </c>
       <c r="R32" t="n">
-        <v>7179851</v>
+        <v>7179686</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4541,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4495,7 +4551,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4542,10 +4598,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129115891</v>
+        <v>129115920</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4577,10 +4633,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529983</v>
+        <v>529936</v>
       </c>
       <c r="R33" t="n">
-        <v>7179662</v>
+        <v>7179647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4612,7 +4668,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4622,7 +4678,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4669,10 +4725,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129115856</v>
+        <v>129115921</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,39 +4736,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529991</v>
+        <v>529933</v>
       </c>
       <c r="R34" t="n">
-        <v>7179662</v>
+        <v>7179634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,7 +4795,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4754,12 +4805,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4770,6 +4821,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4786,10 +4852,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129115859</v>
+        <v>129115922</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4797,39 +4863,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>530097</v>
+        <v>529936</v>
       </c>
       <c r="R35" t="n">
-        <v>7179880</v>
+        <v>7179603</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4861,7 +4922,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4871,12 +4932,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4887,6 +4948,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4903,32 +4979,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129115885</v>
+        <v>129115923</v>
       </c>
       <c r="B36" t="n">
-        <v>80184</v>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4938,10 +5014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529943</v>
+        <v>529957</v>
       </c>
       <c r="R36" t="n">
-        <v>7179577</v>
+        <v>7179580</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4973,7 +5049,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4983,12 +5059,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5030,10 +5106,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129115860</v>
+        <v>129115924</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5041,39 +5117,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>530141</v>
+        <v>529939</v>
       </c>
       <c r="R37" t="n">
-        <v>7179893</v>
+        <v>7179590</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5105,7 +5176,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5115,12 +5186,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5131,6 +5202,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5147,32 +5233,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129115926</v>
+        <v>129115925</v>
       </c>
       <c r="B38" t="n">
-        <v>92360</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5182,10 +5268,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>530129</v>
+        <v>529940</v>
       </c>
       <c r="R38" t="n">
-        <v>7179716</v>
+        <v>7179623</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,7 +5303,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5227,12 +5313,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal mossig granlåga</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5246,17 +5332,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,48 +5360,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129115893</v>
+        <v>129115877</v>
       </c>
       <c r="B39" t="n">
-        <v>80150</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>530230</v>
+        <v>529899</v>
       </c>
       <c r="R39" t="n">
-        <v>7179884</v>
+        <v>7179626</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5347,7 +5430,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5357,7 +5440,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5371,7 +5454,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5405,32 +5487,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129115881</v>
+        <v>129115879</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>80467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5532,32 +5614,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129115924</v>
+        <v>129115883</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5567,10 +5649,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529939</v>
+        <v>529906</v>
       </c>
       <c r="R41" t="n">
-        <v>7179590</v>
+        <v>7179662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5602,7 +5684,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5612,7 +5694,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5659,10 +5741,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129115931</v>
+        <v>129115885</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5694,10 +5776,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>530134</v>
+        <v>529943</v>
       </c>
       <c r="R42" t="n">
-        <v>7179826</v>
+        <v>7179577</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5729,7 +5811,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5739,7 +5821,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5786,27 +5868,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129115858</v>
+        <v>129115876</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5817,7 +5899,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5826,10 +5908,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>530014</v>
+        <v>530020</v>
       </c>
       <c r="R43" t="n">
-        <v>7179865</v>
+        <v>7179835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5861,7 +5943,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5871,12 +5953,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ljudobs födosökande</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5903,10 +5985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129115897</v>
+        <v>129115856</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5914,34 +5996,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>530101</v>
+        <v>529991</v>
       </c>
       <c r="R44" t="n">
-        <v>7179860</v>
+        <v>7179662</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5973,7 +6060,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5983,12 +6070,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5999,21 +6086,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6030,10 +6102,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129115872</v>
+        <v>129115857</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6061,7 +6133,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6070,10 +6142,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>530030</v>
+        <v>529996</v>
       </c>
       <c r="R45" t="n">
-        <v>7179843</v>
+        <v>7179837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6105,7 +6177,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6115,12 +6187,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6147,10 +6219,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129115857</v>
+        <v>129115858</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6178,7 +6250,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6187,10 +6259,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529996</v>
+        <v>530014</v>
       </c>
       <c r="R46" t="n">
-        <v>7179837</v>
+        <v>7179865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6222,7 +6294,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6232,12 +6304,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6264,10 +6336,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129115865</v>
+        <v>129115859</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6295,7 +6367,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6304,10 +6376,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>530131</v>
+        <v>530097</v>
       </c>
       <c r="R47" t="n">
-        <v>7179805</v>
+        <v>7179880</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6339,7 +6411,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6349,12 +6421,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6381,10 +6453,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129115888</v>
+        <v>129115865</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6392,34 +6464,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529919</v>
+        <v>530131</v>
       </c>
       <c r="R48" t="n">
-        <v>7179636</v>
+        <v>7179805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6451,7 +6528,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6461,12 +6538,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6477,21 +6554,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6508,10 +6570,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129115912</v>
+        <v>129115866</v>
       </c>
       <c r="B49" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6519,34 +6581,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>530071</v>
+        <v>530122</v>
       </c>
       <c r="R49" t="n">
-        <v>7179681</v>
+        <v>7179838</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6578,7 +6645,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6588,12 +6655,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6604,21 +6671,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6635,10 +6687,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129115878</v>
+        <v>129115867</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6646,34 +6698,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529899</v>
+        <v>530121</v>
       </c>
       <c r="R50" t="n">
-        <v>7179626</v>
+        <v>7179847</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6705,7 +6762,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6715,12 +6772,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6731,21 +6788,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6762,10 +6804,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129115895</v>
+        <v>129115868</v>
       </c>
       <c r="B51" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6773,34 +6815,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>530122</v>
+        <v>530106</v>
       </c>
       <c r="R51" t="n">
-        <v>7179836</v>
+        <v>7179856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6832,7 +6879,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6842,12 +6889,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Synobs bild födosökande</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6858,21 +6905,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6889,10 +6921,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129115899</v>
+        <v>129115869</v>
       </c>
       <c r="B52" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6900,34 +6932,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>530013</v>
+        <v>530007</v>
       </c>
       <c r="R52" t="n">
-        <v>7179829</v>
+        <v>7179831</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6959,7 +6996,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6969,12 +7006,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6985,21 +7022,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7016,10 +7038,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129115930</v>
+        <v>129115871</v>
       </c>
       <c r="B53" t="n">
-        <v>91573</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7027,30 +7049,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>530065</v>
+        <v>530010</v>
       </c>
       <c r="R53" t="n">
-        <v>7179830</v>
+        <v>7179829</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7082,7 +7113,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7092,12 +7123,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På död stående gran</t>
+          <t>Synobs födosökande</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7108,21 +7139,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7139,10 +7155,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129115887</v>
+        <v>129115872</v>
       </c>
       <c r="B54" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7150,34 +7166,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529887</v>
+        <v>530030</v>
       </c>
       <c r="R54" t="n">
-        <v>7179641</v>
+        <v>7179843</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7209,7 +7230,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7219,12 +7240,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7235,21 +7256,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7266,10 +7272,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129115896</v>
+        <v>129115874</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7277,34 +7283,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>530106</v>
+        <v>530014</v>
       </c>
       <c r="R55" t="n">
-        <v>7179857</v>
+        <v>7179668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7336,7 +7350,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7346,12 +7360,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7362,21 +7376,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7393,10 +7392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129115927</v>
+        <v>129115875</v>
       </c>
       <c r="B56" t="n">
-        <v>91549</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7404,34 +7403,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>530130</v>
+        <v>529938</v>
       </c>
       <c r="R56" t="n">
-        <v>7179707</v>
+        <v>7179691</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7463,7 +7467,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7473,12 +7477,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På granstubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7489,21 +7493,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7520,10 +7509,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129115884</v>
+        <v>129115893</v>
       </c>
       <c r="B57" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7549,16 +7538,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529906</v>
+        <v>530230</v>
       </c>
       <c r="R57" t="n">
-        <v>7179662</v>
+        <v>7179884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7590,7 +7582,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7600,7 +7592,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -7614,6 +7606,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7647,10 +7640,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129115908</v>
+        <v>129115904</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7682,10 +7675,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>530106</v>
+        <v>530147</v>
       </c>
       <c r="R58" t="n">
-        <v>7179677</v>
+        <v>7179724</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7717,7 +7710,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7727,7 +7720,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7774,32 +7767,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129115919</v>
+        <v>129115853</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>92632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7809,10 +7802,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529917</v>
+        <v>530213</v>
       </c>
       <c r="R59" t="n">
-        <v>7179686</v>
+        <v>7179861</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7844,7 +7837,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7854,12 +7847,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På knäckt gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7873,17 +7866,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7901,50 +7894,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129115867</v>
+        <v>129115931</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>80467</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>530121</v>
+        <v>530134</v>
       </c>
       <c r="R60" t="n">
-        <v>7179847</v>
+        <v>7179826</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7976,7 +7964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7986,12 +7974,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8002,6 +7990,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8018,10 +8021,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129115855</v>
+        <v>129115854</v>
       </c>
       <c r="B61" t="n">
-        <v>57735</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8061,10 +8064,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>530228</v>
+        <v>530226</v>
       </c>
       <c r="R61" t="n">
-        <v>7179919</v>
+        <v>7179860</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8096,7 +8099,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8106,12 +8109,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Bohål gran</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8138,10 +8141,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129115874</v>
+        <v>129115855</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8171,7 +8174,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8181,10 +8184,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>530014</v>
+        <v>530228</v>
       </c>
       <c r="R62" t="n">
-        <v>7179668</v>
+        <v>7179919</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8216,7 +8219,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8226,12 +8229,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Bohål gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8258,45 +8261,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129115928</v>
+        <v>129115860</v>
       </c>
       <c r="B63" t="n">
-        <v>91960</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Ytter-rissjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>530065</v>
+        <v>530141</v>
       </c>
       <c r="R63" t="n">
-        <v>7179830</v>
+        <v>7179893</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8328,7 +8336,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8338,12 +8346,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal granticka. Verifierad med mikroskopi av Isak Wahlström.</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8352,7 +8360,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8368,6 +8375,357 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129115861</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ytter-rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>530252</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7179910</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129115862</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ytter-rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>530266</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7179921</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129115864</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ytter-rissjön, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>530219</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7179873</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22116-2025 artfynd.xlsx
+++ b/artfynd/A 22116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115927</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115928</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115878</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115881</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1420,6 +1450,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115884</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115886</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1674,6 +1714,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115887</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115888</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1928,6 +1978,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115890</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2055,6 +2110,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115891</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2182,6 +2242,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115892</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2313,6 +2378,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115893</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2440,6 +2510,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115895</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2567,6 +2642,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115896</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2694,6 +2774,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115897</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2821,6 +2906,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115898</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2948,6 +3038,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115899</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3075,6 +3170,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115900</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3202,6 +3302,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115901</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3329,6 +3434,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115902</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3456,6 +3566,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115903</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3583,6 +3698,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115904</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3710,6 +3830,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115905</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3837,6 +3962,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115907</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3964,6 +4094,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115908</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4091,6 +4226,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115910</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4218,6 +4358,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115912</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4345,6 +4490,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115913</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4472,6 +4622,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115915</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4599,6 +4754,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115916</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4726,6 +4886,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4853,6 +5018,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115919</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4980,6 +5150,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115920</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5107,6 +5282,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115921</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5234,6 +5414,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115922</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5361,6 +5546,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115923</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5488,6 +5678,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115924</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5615,6 +5810,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115853</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5742,6 +5942,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115925</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5869,6 +6074,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115877</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5996,6 +6206,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115879</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6123,6 +6338,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115883</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6250,6 +6470,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115885</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6377,6 +6602,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115931</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6494,6 +6724,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115876</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6614,6 +6849,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115854</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6734,6 +6974,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115855</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6851,6 +7096,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115856</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6968,6 +7218,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115857</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7085,6 +7340,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115858</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7202,6 +7462,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115859</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7319,6 +7584,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115860</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7436,6 +7706,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115861</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7553,6 +7828,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115862</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7670,6 +7950,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115864</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7787,6 +8072,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115865</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7904,6 +8194,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115866</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8021,6 +8316,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115867</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8138,6 +8438,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115868</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8255,6 +8560,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115869</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8372,6 +8682,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115871</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8489,6 +8804,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115872</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8609,6 +8929,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115874</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8726,8 +9051,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115875</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>